--- a/BOM_대량등록_양식.xlsx
+++ b/BOM_대량등록_양식.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\마누스 자재관리 어플개발\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\클로드 코워크\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{495605AA-4080-4368-B86E-7FEB769B2625}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C271D829-488A-4549-8E51-22E0D35C0B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3390" yWindow="0" windowWidth="18645" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM등록" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="331">
   <si>
     <t>BOM 대량 등록/업데이트 양식</t>
   </si>
@@ -776,151 +776,166 @@
     <t>샤워헤드 몸통_연마</t>
   </si>
   <si>
-    <t>QAC004</t>
-  </si>
-  <si>
-    <t>QAC002</t>
-  </si>
-  <si>
-    <t>QAB001</t>
-  </si>
-  <si>
-    <t>11400CO</t>
-  </si>
-  <si>
-    <t>11400NO</t>
-  </si>
-  <si>
-    <t>11400NO-D</t>
-  </si>
-  <si>
-    <t>11401CO</t>
-  </si>
-  <si>
-    <t>11401NO</t>
-  </si>
-  <si>
-    <t>11401NO-D</t>
-  </si>
-  <si>
-    <t>12008NO</t>
-  </si>
-  <si>
-    <t>12054NO</t>
-  </si>
-  <si>
-    <t>12055NO</t>
-  </si>
-  <si>
-    <t>18008NO</t>
-  </si>
-  <si>
-    <t>21006CO-E</t>
-  </si>
-  <si>
-    <t>21006NO</t>
-  </si>
-  <si>
-    <t>21006NO-C</t>
-  </si>
-  <si>
-    <t>21006NO-D</t>
-  </si>
-  <si>
-    <t>21006NO-S</t>
-  </si>
-  <si>
-    <t>21195CO-E</t>
-  </si>
-  <si>
-    <t>21195NO-1</t>
-  </si>
-  <si>
-    <t>21195NO-D</t>
-  </si>
-  <si>
-    <t>22006CO-E</t>
-  </si>
-  <si>
-    <t>22006NO</t>
-  </si>
-  <si>
-    <t>22097NO</t>
-  </si>
-  <si>
-    <t>22098NO</t>
-  </si>
-  <si>
-    <t>22100NO</t>
-  </si>
-  <si>
-    <t>23061NO</t>
-  </si>
-  <si>
-    <t>23186NO</t>
-  </si>
-  <si>
-    <t>23199NO</t>
-  </si>
-  <si>
-    <t>24051CO-E</t>
-  </si>
-  <si>
-    <t>24051CO</t>
-  </si>
-  <si>
-    <t>24051NO-D</t>
-  </si>
-  <si>
-    <t>25016NO</t>
-  </si>
-  <si>
-    <t>31014BA</t>
-  </si>
-  <si>
-    <t>31014RA</t>
-  </si>
-  <si>
-    <t>31024BA</t>
-  </si>
-  <si>
-    <t>31024RA</t>
-  </si>
-  <si>
-    <t>31058BA</t>
-  </si>
-  <si>
-    <t>31058RA</t>
-  </si>
-  <si>
-    <t>33009NA</t>
-  </si>
-  <si>
-    <t>41029NO</t>
-  </si>
-  <si>
-    <t>41627NO</t>
-  </si>
-  <si>
-    <t>41630NO</t>
-  </si>
-  <si>
-    <t>41655NO</t>
+    <t>41607NO</t>
+  </si>
+  <si>
+    <t>72017NO</t>
+  </si>
+  <si>
+    <t>74023NO</t>
+  </si>
+  <si>
+    <t>LF8200TNAE</t>
+  </si>
+  <si>
+    <t>11076NO</t>
+  </si>
+  <si>
+    <t>11077NO</t>
+  </si>
+  <si>
+    <t>11078NO</t>
+  </si>
+  <si>
+    <t>11080NO</t>
+  </si>
+  <si>
+    <t>11083KA</t>
+  </si>
+  <si>
+    <t>11324NO</t>
+  </si>
+  <si>
+    <t>12017NO</t>
+  </si>
+  <si>
+    <t>21064NO</t>
+  </si>
+  <si>
+    <t>21064NO-C</t>
+  </si>
+  <si>
+    <t>21064NO-K</t>
+  </si>
+  <si>
+    <t>22026NO</t>
+  </si>
+  <si>
+    <t>23086CO</t>
+  </si>
+  <si>
+    <t>23086CO-E</t>
+  </si>
+  <si>
+    <t>41603NO</t>
+  </si>
+  <si>
+    <t>43017NO</t>
+  </si>
+  <si>
+    <t>62004CA</t>
+  </si>
+  <si>
+    <t>71004IN</t>
+  </si>
+  <si>
+    <t>71004ON</t>
+  </si>
+  <si>
+    <t>72003NO</t>
+  </si>
+  <si>
+    <t>73005XO</t>
+  </si>
+  <si>
+    <t>73005YO</t>
+  </si>
+  <si>
+    <t>74143NO</t>
+  </si>
+  <si>
+    <t>74187NO</t>
+  </si>
+  <si>
+    <t>LF17KM</t>
+  </si>
+  <si>
+    <t>11083KO</t>
+  </si>
+  <si>
+    <t>11091KO</t>
+  </si>
+  <si>
+    <t>13001NO</t>
+  </si>
+  <si>
+    <t>21071CO-E</t>
+  </si>
+  <si>
+    <t>21071NO</t>
+  </si>
+  <si>
+    <t>21071NO-C</t>
+  </si>
+  <si>
+    <t>21071NO-D</t>
+  </si>
+  <si>
+    <t>21071NO-K</t>
+  </si>
+  <si>
+    <t>22001NO</t>
+  </si>
+  <si>
+    <t>22004NO</t>
+  </si>
+  <si>
+    <t>41010NO</t>
+  </si>
+  <si>
+    <t>41060NO</t>
+  </si>
+  <si>
+    <t>43007NO</t>
   </si>
   <si>
     <t>51007NO</t>
   </si>
   <si>
-    <t>51051NO-1</t>
-  </si>
-  <si>
-    <t>51141NO</t>
-  </si>
-  <si>
-    <t>51146NO</t>
-  </si>
-  <si>
-    <t>62004CA</t>
+    <t>51112NO</t>
+  </si>
+  <si>
+    <t>52004CO</t>
+  </si>
+  <si>
+    <t>61031NA</t>
+  </si>
+  <si>
+    <t>62040CA</t>
+  </si>
+  <si>
+    <t>71008IN</t>
+  </si>
+  <si>
+    <t>71008ON</t>
+  </si>
+  <si>
+    <t>72001NO</t>
+  </si>
+  <si>
+    <t>74002NO</t>
+  </si>
+  <si>
+    <t>74014NO</t>
+  </si>
+  <si>
+    <t>LF1500CA</t>
+  </si>
+  <si>
+    <t>01016CA</t>
+  </si>
+  <si>
+    <t>11296KO</t>
   </si>
   <si>
     <t>71853NO</t>
@@ -929,28 +944,88 @@
     <t>71854NO</t>
   </si>
   <si>
-    <t>71855NO</t>
-  </si>
-  <si>
-    <t>73061XO</t>
-  </si>
-  <si>
-    <t>73061YO</t>
-  </si>
-  <si>
-    <t>73062XO</t>
-  </si>
-  <si>
-    <t>73062YO</t>
-  </si>
-  <si>
-    <t>74014NO</t>
-  </si>
-  <si>
-    <t>74021NO</t>
-  </si>
-  <si>
-    <t>74092NO</t>
+    <t>73097NO</t>
+  </si>
+  <si>
+    <t>73098NO</t>
+  </si>
+  <si>
+    <t>CF248KMN</t>
+  </si>
+  <si>
+    <t>11030CO</t>
+  </si>
+  <si>
+    <t>11065CO</t>
+  </si>
+  <si>
+    <t>21062CO-E</t>
+  </si>
+  <si>
+    <t>21062NO</t>
+  </si>
+  <si>
+    <t>21062NO-C</t>
+  </si>
+  <si>
+    <t>21062NO-K</t>
+  </si>
+  <si>
+    <t>22012CO</t>
+  </si>
+  <si>
+    <t>23003CO</t>
+  </si>
+  <si>
+    <t>23009BO</t>
+  </si>
+  <si>
+    <t>23009CO-E</t>
+  </si>
+  <si>
+    <t>23009NO</t>
+  </si>
+  <si>
+    <t>23041CO</t>
+  </si>
+  <si>
+    <t>23042CO</t>
+  </si>
+  <si>
+    <t>23043CO-E</t>
+  </si>
+  <si>
+    <t>23043NO</t>
+  </si>
+  <si>
+    <t>23043NO-D</t>
+  </si>
+  <si>
+    <t>41013NO</t>
+  </si>
+  <si>
+    <t>41611NO</t>
+  </si>
+  <si>
+    <t>41615NO</t>
+  </si>
+  <si>
+    <t>42002NO</t>
+  </si>
+  <si>
+    <t>42003NO</t>
+  </si>
+  <si>
+    <t>51009NO</t>
+  </si>
+  <si>
+    <t>51051NO</t>
+  </si>
+  <si>
+    <t>71635IN</t>
+  </si>
+  <si>
+    <t>71635ON</t>
   </si>
 </sst>
 </file>
@@ -1378,7 +1453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
@@ -1425,10 +1500,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -1438,10 +1513,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
@@ -1451,10 +1526,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -1464,10 +1539,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -1477,10 +1552,10 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1490,10 +1565,10 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>256</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1501,10 +1576,10 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B10" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1512,21 +1587,21 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B11" t="s">
-        <v>232</v>
+        <v>45</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B12" t="s">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1534,10 +1609,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B13" t="s">
-        <v>214</v>
+        <v>259</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1545,10 +1620,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B14" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1556,10 +1631,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B15" t="s">
-        <v>214</v>
+        <v>87</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1567,21 +1642,21 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B16" t="s">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B17" t="s">
-        <v>234</v>
+        <v>262</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1589,10 +1664,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B18" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1600,10 +1675,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B19" t="s">
-        <v>227</v>
+        <v>108</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1611,32 +1686,32 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B20" t="s">
-        <v>227</v>
+        <v>264</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B21" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B22" t="s">
-        <v>216</v>
+        <v>265</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1644,10 +1719,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1655,10 +1730,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s">
-        <v>216</v>
+        <v>163</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1666,10 +1741,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1677,10 +1752,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1688,21 +1763,21 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1710,10 +1785,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -1721,10 +1796,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B30" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -1732,10 +1807,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B31" t="s">
-        <v>256</v>
+        <v>198</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1743,21 +1818,21 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>272</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B33" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1765,10 +1840,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="B34" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -1776,21 +1851,21 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>276</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>277</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -1798,10 +1873,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s">
-        <v>80</v>
+        <v>278</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -1809,10 +1884,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1820,10 +1895,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>280</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -1831,10 +1906,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="B40" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -1842,10 +1917,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="B41" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -1853,10 +1928,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="B42" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -1864,10 +1939,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="B43" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -1875,10 +1950,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="B44" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -1886,10 +1961,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="B45" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -1897,10 +1972,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="B46" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -1908,10 +1983,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="B47" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -1919,10 +1994,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="B48" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -1930,10 +2005,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="B49" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -1941,10 +2016,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="B50" t="s">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -1952,10 +2027,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="B51" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -1963,10 +2038,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="B52" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -1974,10 +2049,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="B53" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -1985,21 +2060,21 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="B54" t="s">
-        <v>266</v>
+        <v>294</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>3.3000000000000002E-2</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="B55" t="s">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -2007,10 +2082,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="B56" t="s">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -2018,21 +2093,21 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="B57" t="s">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>3.3000000000000002E-2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="B58" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -2040,10 +2115,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>247</v>
+        <v>298</v>
       </c>
       <c r="B59" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -2051,10 +2126,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="B60" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -2062,10 +2137,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>247</v>
+        <v>298</v>
       </c>
       <c r="B61" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -2073,10 +2148,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="B62" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -2084,10 +2159,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="B63" t="s">
-        <v>87</v>
+        <v>301</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -2095,21 +2170,21 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="B64" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="B65" t="s">
-        <v>271</v>
+        <v>177</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -2117,10 +2192,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="B66" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -2128,21 +2203,21 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="B67" t="s">
-        <v>93</v>
+        <v>303</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>247</v>
+        <v>298</v>
       </c>
       <c r="B68" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -2150,10 +2225,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>248</v>
+        <v>298</v>
       </c>
       <c r="B69" t="s">
-        <v>273</v>
+        <v>198</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -2161,10 +2236,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="B70" t="s">
-        <v>274</v>
+        <v>207</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -2172,10 +2247,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="B71" t="s">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -2183,10 +2258,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="B72" t="s">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -2194,10 +2269,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="B73" t="s">
-        <v>277</v>
+        <v>307</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -2205,10 +2280,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="B74" t="s">
-        <v>278</v>
+        <v>45</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -2216,10 +2291,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B75" t="s">
-        <v>279</v>
+        <v>308</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -2227,10 +2302,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>248</v>
+        <v>305</v>
       </c>
       <c r="B76" t="s">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -2238,10 +2313,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>248</v>
+        <v>305</v>
       </c>
       <c r="B77" t="s">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -2249,10 +2324,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B78" t="s">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -2260,10 +2335,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B79" t="s">
-        <v>283</v>
+        <v>312</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -2271,10 +2346,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="B80" t="s">
-        <v>284</v>
+        <v>313</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -2282,10 +2357,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="B81" t="s">
-        <v>285</v>
+        <v>314</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -2293,10 +2368,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B82" t="s">
-        <v>286</v>
+        <v>315</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -2304,10 +2379,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="B83" t="s">
-        <v>108</v>
+        <v>316</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -2315,10 +2390,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>248</v>
+        <v>305</v>
       </c>
       <c r="B84" t="s">
-        <v>108</v>
+        <v>317</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -2326,10 +2401,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B85" t="s">
-        <v>108</v>
+        <v>318</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -2337,10 +2412,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B86" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -2348,10 +2423,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B87" t="s">
-        <v>111</v>
+        <v>320</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -2359,10 +2434,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="B88" t="s">
-        <v>117</v>
+        <v>321</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -2370,10 +2445,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>248</v>
+        <v>305</v>
       </c>
       <c r="B89" t="s">
-        <v>117</v>
+        <v>322</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -2381,10 +2456,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B90" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -2392,21 +2467,21 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B91" t="s">
-        <v>124</v>
+        <v>323</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B92" t="s">
-        <v>127</v>
+        <v>324</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -2414,54 +2489,54 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B93" t="s">
-        <v>130</v>
+        <v>325</v>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B94" t="s">
-        <v>136</v>
+        <v>326</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="B95" t="s">
-        <v>288</v>
+        <v>327</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>248</v>
+        <v>305</v>
       </c>
       <c r="B96" t="s">
-        <v>288</v>
+        <v>328</v>
       </c>
       <c r="C96">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="B97" t="s">
-        <v>289</v>
+        <v>329</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -2469,21 +2544,21 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>248</v>
+        <v>305</v>
       </c>
       <c r="B98" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>2.7E-2</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B99" t="s">
-        <v>144</v>
+        <v>295</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -2491,651 +2566,13 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
       <c r="B100" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>247</v>
-      </c>
-      <c r="B101" t="s">
-        <v>149</v>
-      </c>
-      <c r="C101">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>248</v>
-      </c>
-      <c r="B102" t="s">
-        <v>149</v>
-      </c>
-      <c r="C102">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>249</v>
-      </c>
-      <c r="B103" t="s">
-        <v>149</v>
-      </c>
-      <c r="C103">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>247</v>
-      </c>
-      <c r="B104" t="s">
-        <v>291</v>
-      </c>
-      <c r="C104">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>248</v>
-      </c>
-      <c r="B105" t="s">
-        <v>291</v>
-      </c>
-      <c r="C105">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>249</v>
-      </c>
-      <c r="B106" t="s">
-        <v>292</v>
-      </c>
-      <c r="C106">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>247</v>
-      </c>
-      <c r="B107" t="s">
-        <v>152</v>
-      </c>
-      <c r="C107">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>248</v>
-      </c>
-      <c r="B108" t="s">
-        <v>152</v>
-      </c>
-      <c r="C108">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>249</v>
-      </c>
-      <c r="B109" t="s">
-        <v>152</v>
-      </c>
-      <c r="C109">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>247</v>
-      </c>
-      <c r="B110" t="s">
-        <v>114</v>
-      </c>
-      <c r="C110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>248</v>
-      </c>
-      <c r="B111" t="s">
-        <v>114</v>
-      </c>
-      <c r="C111">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>249</v>
-      </c>
-      <c r="B112" t="s">
-        <v>114</v>
-      </c>
-      <c r="C112">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>249</v>
-      </c>
-      <c r="B113" t="s">
-        <v>155</v>
-      </c>
-      <c r="C113">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>249</v>
-      </c>
-      <c r="B114" t="s">
-        <v>158</v>
-      </c>
-      <c r="C114">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>249</v>
-      </c>
-      <c r="B115" t="s">
-        <v>293</v>
-      </c>
-      <c r="C115">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>249</v>
-      </c>
-      <c r="B116" t="s">
-        <v>294</v>
-      </c>
-      <c r="C116">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>247</v>
-      </c>
-      <c r="B117" t="s">
-        <v>163</v>
-      </c>
-      <c r="C117">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>248</v>
-      </c>
-      <c r="B118" t="s">
-        <v>163</v>
-      </c>
-      <c r="C118">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>249</v>
-      </c>
-      <c r="B119" t="s">
-        <v>163</v>
-      </c>
-      <c r="C119">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>247</v>
-      </c>
-      <c r="B120" t="s">
-        <v>295</v>
-      </c>
-      <c r="C120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>248</v>
-      </c>
-      <c r="B121" t="s">
-        <v>295</v>
-      </c>
-      <c r="C121">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>249</v>
-      </c>
-      <c r="B122" t="s">
-        <v>295</v>
-      </c>
-      <c r="C122">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>247</v>
-      </c>
-      <c r="B123" t="s">
-        <v>296</v>
-      </c>
-      <c r="C123">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>248</v>
-      </c>
-      <c r="B124" t="s">
-        <v>296</v>
-      </c>
-      <c r="C124">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>249</v>
-      </c>
-      <c r="B125" t="s">
-        <v>296</v>
-      </c>
-      <c r="C125">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>247</v>
-      </c>
-      <c r="B126" t="s">
-        <v>297</v>
-      </c>
-      <c r="C126">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>248</v>
-      </c>
-      <c r="B127" t="s">
-        <v>297</v>
-      </c>
-      <c r="C127">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>249</v>
-      </c>
-      <c r="B128" t="s">
-        <v>297</v>
-      </c>
-      <c r="C128">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>247</v>
-      </c>
-      <c r="B129" t="s">
-        <v>298</v>
-      </c>
-      <c r="C129">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>248</v>
-      </c>
-      <c r="B130" t="s">
-        <v>298</v>
-      </c>
-      <c r="C130">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>249</v>
-      </c>
-      <c r="B131" t="s">
-        <v>298</v>
-      </c>
-      <c r="C131">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>247</v>
-      </c>
-      <c r="B132" t="s">
-        <v>177</v>
-      </c>
-      <c r="C132">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>248</v>
-      </c>
-      <c r="B133" t="s">
-        <v>177</v>
-      </c>
-      <c r="C133">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>249</v>
-      </c>
-      <c r="B134" t="s">
-        <v>177</v>
-      </c>
-      <c r="C134">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>249</v>
-      </c>
-      <c r="B135" t="s">
-        <v>299</v>
-      </c>
-      <c r="C135">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>249</v>
-      </c>
-      <c r="B136" t="s">
-        <v>300</v>
-      </c>
-      <c r="C136">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>247</v>
-      </c>
-      <c r="B137" t="s">
-        <v>301</v>
-      </c>
-      <c r="C137">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>248</v>
-      </c>
-      <c r="B138" t="s">
-        <v>301</v>
-      </c>
-      <c r="C138">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>247</v>
-      </c>
-      <c r="B139" t="s">
-        <v>302</v>
-      </c>
-      <c r="C139">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>248</v>
-      </c>
-      <c r="B140" t="s">
-        <v>302</v>
-      </c>
-      <c r="C140">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>247</v>
-      </c>
-      <c r="B141" t="s">
-        <v>303</v>
-      </c>
-      <c r="C141">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>248</v>
-      </c>
-      <c r="B142" t="s">
-        <v>303</v>
-      </c>
-      <c r="C142">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>249</v>
-      </c>
-      <c r="B143" t="s">
-        <v>303</v>
-      </c>
-      <c r="C143">
-        <v>0.125</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>247</v>
-      </c>
-      <c r="B144" t="s">
-        <v>304</v>
-      </c>
-      <c r="C144">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>248</v>
-      </c>
-      <c r="B145" t="s">
-        <v>304</v>
-      </c>
-      <c r="C145">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>247</v>
-      </c>
-      <c r="B146" t="s">
-        <v>198</v>
-      </c>
-      <c r="C146">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>248</v>
-      </c>
-      <c r="B147" t="s">
-        <v>198</v>
-      </c>
-      <c r="C147">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>249</v>
-      </c>
-      <c r="B148" t="s">
-        <v>198</v>
-      </c>
-      <c r="C148">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>247</v>
-      </c>
-      <c r="B149" t="s">
-        <v>305</v>
-      </c>
-      <c r="C149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>248</v>
-      </c>
-      <c r="B150" t="s">
-        <v>305</v>
-      </c>
-      <c r="C150">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>249</v>
-      </c>
-      <c r="B151" t="s">
-        <v>305</v>
-      </c>
-      <c r="C151">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>247</v>
-      </c>
-      <c r="B152" t="s">
-        <v>207</v>
-      </c>
-      <c r="C152">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>248</v>
-      </c>
-      <c r="B153" t="s">
-        <v>207</v>
-      </c>
-      <c r="C153">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>249</v>
-      </c>
-      <c r="B154" t="s">
-        <v>207</v>
-      </c>
-      <c r="C154">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>247</v>
-      </c>
-      <c r="B155" t="s">
-        <v>210</v>
-      </c>
-      <c r="C155">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>248</v>
-      </c>
-      <c r="B156" t="s">
-        <v>210</v>
-      </c>
-      <c r="C156">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
-        <v>249</v>
-      </c>
-      <c r="B157" t="s">
-        <v>210</v>
-      </c>
-      <c r="C157">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>249</v>
-      </c>
-      <c r="B158" t="s">
-        <v>204</v>
-      </c>
-      <c r="C158">
-        <v>1</v>
+        <v>2.7E-2</v>
       </c>
     </row>
   </sheetData>
